--- a/downloads/purchasing/dixani-request-for-quotation-rfq.xlsx
+++ b/downloads/purchasing/dixani-request-for-quotation-rfq.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFQ" sheetId="1" r:id="R5aac6de7d7474cdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="Rbb378e50c98f4cb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFQ" sheetId="1" r:id="Rcfe6c097b4b04d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="2" r:id="R24633752643f4a1a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -482,7 +482,9 @@
       <x:c r="D6" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="E6"/>
+      <x:c r="E6" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="F6"/>
       <x:c r="G6" t="str">
         <x:v>Quotation Validity</x:v>
@@ -1311,7 +1313,7 @@
   </x:mergeCells>
   <x:dataValidations count="6">
     <x:dataValidation type="list" sqref="E6">
-      <x:formula1>"QAR,USD,EUR,GBP,AED,SAR,LKR,INR"</x:formula1>
+      <x:formula1>"USD,EUR,GBP,CAD,AUD,NZD,CHF,JPY,CNY,HKD,SGD,INR,AED,SAR,QAR,LKR,ZAR,BRL,MXN"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E15:E34">
       <x:formula1>"PCS,EA,BOX,CTN,KG,G,L,ML,M,SET,PACK,PAIR,HOUR,SERVICE"</x:formula1>
